--- a/ExcelTable/Core.xlsx
+++ b/ExcelTable/Core.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BaseBetRegions" sheetId="1" r:id="Ra8255d78c51c4d65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SlotSymbols" sheetId="2" r:id="R92fcc586bc904ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paytable" sheetId="3" r:id="R08973cac17794d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paylines" sheetId="4" r:id="R269630bd21cb43c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multipliers" sheetId="5" r:id="Reebef2a77c9a4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BaseBetRegions" sheetId="1" r:id="R2163c3e1357f47dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SlotSymbols" sheetId="2" r:id="Rf56d177920884772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paytable" sheetId="3" r:id="R6fb756563c46465f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paylines" sheetId="4" r:id="R07a37bea2256482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multipliers" sheetId="5" r:id="Rda28840e3a504a0c"/>
   </x:sheets>
 </x:workbook>
 </file>
